--- a/Кафе_Учет.xlsx
+++ b/Кафе_Учет.xlsx
@@ -13,6 +13,9 @@
     <sheet name="ФУДКОСТ" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="P&amp;L" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ABC_АНАЛИЗ" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="КАТЕГОРИИ" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ПОДКАТЕГОРИИ" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="КАТЕГОРИИ_ПОЛНАЯ" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -431,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,7 +519,6 @@
           <t>Карта</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -553,7 +555,6 @@
           <t>Наличные</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -590,7 +591,6 @@
           <t>Карта</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -627,7 +627,6 @@
           <t>Карта</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -664,7 +663,6 @@
           <t>Наличные</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -672,14 +670,6 @@
           <t>ИТОГО за день:</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -687,14 +677,6 @@
           <t>Средний чек:</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -731,7 +713,6 @@
           <t>Наличные</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -768,7 +749,6 @@
           <t>Наличные</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -805,7 +785,1256 @@
           <t>Наличные</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Анна</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Капучино, Чизкейк, Пицца Маргарита</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Наличные</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Основная категория</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Подкатегория</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Блюдо</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Цена (₸)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Себестоимость (₸)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Горячие напитки</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Капучино</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Горячие напитки</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Латте</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Горячие напитки</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Американо</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Горячие напитки</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Эспрессо</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Холодные напитки</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Чай холодный</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Холодные напитки</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Лимонад</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Холодные напитки</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Морс</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Соки</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Апельсиновый</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Соки</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Яблочный</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Соки</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Мультифрукт</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Шашлыки</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Шашлык из курицы</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Куриный шашлык</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Шашлыки</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Шашлык из курицы</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Крылышки гриль</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Шашлыки</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Шашлык из говядины</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Говяжий шашлык</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Шашлыки</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Шашлык из говядины</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Люля-кебаб</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Шашлыки</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Шашлык из свинины</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Свиной шашлык</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Шашлыки</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Шашлык из свинины</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Корейка гриль</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Классическая</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Маргарита</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Классическая</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Пепперони</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Мясная</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Карбонара</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Мясная</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Мясное ассорти</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Вегетарианская</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Грибная</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Вегетарианская</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Четыре сыра</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Первые блюда</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Супы</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Суп куриный</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Первые блюда</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Супы</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Борщ</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Первые блюда</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Супы</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Солянка</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Вторые блюда</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Гарниры</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Рис</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Вторые блюда</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Гарниры</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Картофель фри</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Вторые блюда</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Гарниры</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Пюре</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Вторые блюда</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Мясные</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Стейк</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Вторые блюда</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Мясные</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Котлета по-киевски</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Бургеры</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Чизбургер</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Бургеры</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Гамбургер</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Закуски</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Картошка фри</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Закуски</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Наггетсы</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Соусы</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Основные</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Кетчуп</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Соусы</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Основные</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Майонез</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Соусы</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Авторские</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Сырный</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Соусы</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Авторские</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Чесночный</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Донер</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>В лаваше</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Донер классический</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Донер</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>В лаваше</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Донер острый</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Донер</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>В боксе</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Донер-бокс курица</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Выпечка</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Сладкая</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Круассан</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Выпечка</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Сладкая</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Синнабон</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Выпечка</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Солёная</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Слойка с сыром</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Выпечка</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Солёная</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Самса</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Торты</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Чизкейк</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Торты</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Медовик</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Пирожные</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Эклер</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Пирожные</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Картошка</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Мороженое</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Пломбир</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Мороженое</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Шоколадное</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -818,7 +2047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -829,27 +2058,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Ингредиенты</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Себестоимость (₸)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Цена продажи (₸)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Маржинальность (%)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Unnamed: 5</t>
         </is>
       </c>
     </row>
@@ -861,16 +2090,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Кофе, молоко</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>80</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>250</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>68</v>
       </c>
     </row>
@@ -882,16 +2116,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Сыр, печенье</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>120</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>350</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>65.71428571428571</v>
       </c>
     </row>
@@ -903,16 +2142,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Тесто, соус, сыр</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>156</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>550</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>71.63636363636363</v>
       </c>
     </row>
@@ -924,16 +2168,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Первые блюда</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Курица, овощи</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>70</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>280</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>75</v>
       </c>
     </row>
@@ -945,16 +2194,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Выпечка</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Мука, дрожжи</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>25</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>75</v>
       </c>
     </row>
@@ -966,16 +2220,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Кофе, молоко</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>85</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>300</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>71.66666666666667</v>
       </c>
     </row>
@@ -987,16 +2246,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Выпечка</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Мука, масло</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>55</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>200</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>72.5</v>
       </c>
     </row>
@@ -1008,22 +2272,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Чай, вода</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>15</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>100</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>85</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="F10" t="n">
-        <v>73.0646645021645</v>
       </c>
     </row>
   </sheetData>
@@ -2284,4 +3548,1510 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Первые блюда</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Вторые блюда</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Соусы</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Шашлыки</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Донер</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Выпечка</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Мороженое</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C82"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Основная категория</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Подкатегория</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Блюдо</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Горячие напитки</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Капучино</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Горячие напитки</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Латте</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Горячие напитки</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Американо</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Горячие напитки</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Эспрессо</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Горячие напитки</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Глинтвейн</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Холодные напитки</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Чай холодный</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Холодные напитки</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Лимонад</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Холодные напитки</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Морс</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Холодные напитки</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Компот</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Соки</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Апельсиновый</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Соки</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Яблочный</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Соки</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Мультифрукт</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Шашлыки</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Шашлык из курицы</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Куриный шашлык (сочный)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Шашлыки</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Шашлык из курицы</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Крылышки гриль</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Шашлыки</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Шашлык из говядины</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Говяжий шашлык</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Шашлыки</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Шашлык из говядины</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Люля-кебаб из говядины</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Шашлыки</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Шашлык из свинины</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Свиной шашлык (балык)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Шашлыки</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Шашлык из свинины</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Корейка гриль</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Шашлыки</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Овощной шашлык</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Шампиньоны гриль</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Шашлыки</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Овощной шашлык</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Овощи гриль (микс)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Классическая</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Маргарита</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Классическая</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Пепперони</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Классическая</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Гавайская</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Мясная</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Карбонара</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Мясная</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Мясное ассорти</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Вегетарианская</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Грибная</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Вегетарианская</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Четыре сыра</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Пицца</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Вегетарианская</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Вегетарианская</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Первые блюда</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Супы</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Суп куриный</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Первые блюда</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Супы</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Борщ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Первые блюда</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Супы</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Солянка</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Первые блюда</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Супы</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Томатный суп</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Первые блюда</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Бульоны</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Куриный бульон</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Первые блюда</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Бульоны</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Говяжий бульон</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Вторые блюда</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Гарниры</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Рис</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Вторые блюда</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Гарниры</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Картофель фри</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Вторые блюда</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Гарниры</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Картофельное пюре</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Вторые блюда</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Гарниры</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Паста</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Вторые блюда</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Мясные</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Стейк из говядины</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Вторые блюда</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Мясные</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Котлета по-киевски</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Вторые блюда</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Мясные</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Эскалоп</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Вторые блюда</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Рыбные</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Лосось на гриле</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Вторые блюда</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Рыбные</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Треска запечённая</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Бургеры</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Чизбургер</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Бургеры</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Гамбургер</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Бургеры</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Двойной бургер</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Закуски</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Картошка фри</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Закуски</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Наггетсы</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Закуски</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Крылышки</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Хот-доги</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Хот-дог классический</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Фастфуд</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Хот-доги</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Хот-дог сырный</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Соусы</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Основные</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Кетчуп</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Соусы</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Основные</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Майонез</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Соусы</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Основные</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Горчица</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Соусы</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Авторские</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Сырный соус</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Соусы</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Авторские</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Чесночный соус</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Соусы</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Авторские</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Тартар</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Соусы</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Авторские</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Барбекю</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Донер</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>В лаваше</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Донер классический</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Донер</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>В лаваше</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Донер острый</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Донер</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>В лаваше</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Донер сырный</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Донер</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>В боксе</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Донер-бокс курица</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Донер</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>В боксе</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Донер-бокс говядина</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Донер</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Вегетарианский</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Донер овощной</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Донер</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Вегетарианский</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Донер с грибами</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Выпечка</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Сладкая</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Круассан</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Выпечка</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Сладкая</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Синнабон</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Выпечка</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Сладкая</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Маффин</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Выпечка</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Сладкая</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Пончик</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Выпечка</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Солёная</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Пирожок с мясом</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Выпечка</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Солёная</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Слойка с сыром</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Выпечка</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Солёная</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Самса</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Торты</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Чизкейк</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Торты</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Медовик</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Торты</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Наполеон</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Пирожные</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Эклер</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Пирожные</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Картошка</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Пирожные</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Корзинка</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Мороженое</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Пломбир</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Мороженое</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Шоколадное</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Десерты</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Мороженое</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Фруктовый лёд</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Кафе_Учет.xlsx
+++ b/Кафе_Учет.xlsx
@@ -16,6 +16,7 @@
     <sheet name="КАТЕГОРИИ" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="ПОДКАТЕГОРИИ" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="КАТЕГОРИИ_ПОЛНАЯ" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="ПЕРСОНАЛ" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -434,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +520,7 @@
           <t>Карта</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -555,6 +557,7 @@
           <t>Наличные</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -591,6 +594,7 @@
           <t>Карта</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -627,6 +631,7 @@
           <t>Карта</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -663,6 +668,7 @@
           <t>Наличные</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -670,6 +676,14 @@
           <t>ИТОГО за день:</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -677,6 +691,14 @@
           <t>Средний чек:</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -713,6 +735,7 @@
           <t>Наличные</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -749,6 +772,7 @@
           <t>Наличные</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -785,6 +809,7 @@
           <t>Наличные</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -821,6 +846,44 @@
           <t>Наличные</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Мярт</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Латте, Капучино, Суп куриный</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>830</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Наличные</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2034,6 +2097,186 @@
       </c>
       <c r="E52" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Имя</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Должность</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Телефон</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>PIN-код</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Активен</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Дата добавления</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Анна</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Официант</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+7XXX</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1234</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Иван</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Официант</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+7XXX</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5678</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Администратор</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+7XXX</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Мярт</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Официант</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7777</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
